--- a/Tabla7_StandardizedDataWithNewDerivedVariable.xlsx
+++ b/Tabla7_StandardizedDataWithNewDerivedVariable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msamper\Dropbox\LIBRO\Repositorio de datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMILA SAMPER\Dropbox\LIBRO\Repositorio de datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F8C110-C112-4E6C-AB89-0357CE850023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1890DE5F-9357-4822-B3B5-DCBABABE6AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31920" yWindow="2910" windowWidth="21600" windowHeight="11385" xr2:uid="{2DF06FF3-52B9-499B-B0D2-C28FAD31714D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DF06FF3-52B9-499B-B0D2-C28FAD31714D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla 7_Variable derivadas 2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -89,12 +89,6 @@
     <t>Bucaramanga</t>
   </si>
   <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t> NULL</t>
-  </si>
-  <si>
     <t>Grupo de edad</t>
   </si>
   <si>
@@ -120,13 +114,19 @@
   </si>
   <si>
     <t>Trimestre</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t> null</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +275,20 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Avenir Next LT Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Avenir Next LT Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Avenir Next LT Pro"/>
@@ -694,7 +708,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -711,9 +725,6 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -761,6 +772,30 @@
     </xf>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1138,20 +1173,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A08E36C-4A08-44EC-B70C-8187CCD1F91E}">
   <dimension ref="A1:I39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1167,20 +1202,20 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="21" t="s">
+      <c r="F1" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1196,57 +1231,57 @@
       <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="17">
+      <c r="F2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="16">
         <v>2025</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="16">
         <v>12</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13">
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>46018</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="14">
         <v>27</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="18">
+      <c r="F3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="17">
         <v>2025</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="17">
         <v>12</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="17">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4">
         <v>46036</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
+      <c r="C4" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>5</v>
@@ -1254,49 +1289,49 @@
       <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H4" s="17">
-        <v>1</v>
-      </c>
-      <c r="I4" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
+      <c r="F4" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="16">
+        <v>1</v>
+      </c>
+      <c r="I4" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>46037</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="14">
         <v>45</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H5" s="18">
-        <v>1</v>
-      </c>
-      <c r="I5" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="17">
+        <v>1</v>
+      </c>
+      <c r="I5" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1312,49 +1347,49 @@
       <c r="E6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H6" s="17">
-        <v>1</v>
-      </c>
-      <c r="I6" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+      <c r="F6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="16">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>46039</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>29</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H7" s="18">
-        <v>1</v>
-      </c>
-      <c r="I7" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="17">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1367,52 +1402,52 @@
       <c r="D8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H8" s="17">
-        <v>1</v>
-      </c>
-      <c r="I8" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+      <c r="E8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="16">
+        <v>1</v>
+      </c>
+      <c r="I8" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="21">
         <v>46041</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="15" t="s">
+      <c r="C9" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H9" s="18">
-        <v>1</v>
-      </c>
-      <c r="I9" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H9" s="17">
+        <v>1</v>
+      </c>
+      <c r="I9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1428,49 +1463,49 @@
       <c r="E10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H10" s="17">
-        <v>1</v>
-      </c>
-      <c r="I10" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
+      <c r="F10" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="16">
+        <v>1</v>
+      </c>
+      <c r="I10" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>46043</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <v>31</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H11" s="18">
-        <v>1</v>
-      </c>
-      <c r="I11" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="17">
+        <v>1</v>
+      </c>
+      <c r="I11" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1486,49 +1521,49 @@
       <c r="E12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H12" s="17">
-        <v>1</v>
-      </c>
-      <c r="I12" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+      <c r="F12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H12" s="16">
+        <v>1</v>
+      </c>
+      <c r="I12" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>46045</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>55</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H13" s="18">
-        <v>1</v>
-      </c>
-      <c r="I13" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F13" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H13" s="17">
+        <v>1</v>
+      </c>
+      <c r="I13" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1544,49 +1579,49 @@
       <c r="E14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H14" s="17">
-        <v>1</v>
-      </c>
-      <c r="I14" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
+      <c r="F14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1</v>
+      </c>
+      <c r="I14" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <v>46049</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <v>34</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H15" s="18">
-        <v>1</v>
-      </c>
-      <c r="I15" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H15" s="17">
+        <v>1</v>
+      </c>
+      <c r="I15" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1602,49 +1637,49 @@
       <c r="E16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H16" s="17">
-        <v>1</v>
-      </c>
-      <c r="I16" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
+      <c r="F16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H16" s="16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>46051</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>20</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H17" s="18">
-        <v>1</v>
-      </c>
-      <c r="I17" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1660,49 +1695,49 @@
       <c r="E18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H18" s="17">
-        <v>1</v>
-      </c>
-      <c r="I18" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
+      <c r="F18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H18" s="16">
+        <v>1</v>
+      </c>
+      <c r="I18" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>46053</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <v>9</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H19" s="18">
-        <v>1</v>
-      </c>
-      <c r="I19" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H19" s="17">
+        <v>1</v>
+      </c>
+      <c r="I19" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1715,60 +1750,60 @@
       <c r="D20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H20" s="17">
+      <c r="E20" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H20" s="16">
         <v>2</v>
       </c>
-      <c r="I20" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
+      <c r="I20" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <v>46055</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <v>39</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H21" s="18">
+      <c r="F21" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H21" s="17">
         <v>2</v>
       </c>
-      <c r="I21" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4">
         <v>46056</v>
       </c>
-      <c r="C22" s="5">
-        <v>12</v>
+      <c r="C22" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
@@ -1776,49 +1811,49 @@
       <c r="E22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H22" s="17">
+      <c r="F22" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="16">
         <v>2</v>
       </c>
-      <c r="I22" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
+      <c r="I22" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <v>46057</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>25</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H23" s="18">
+      <c r="F23" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H23" s="17">
         <v>2</v>
       </c>
-      <c r="I23" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1834,49 +1869,49 @@
       <c r="E24" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H24" s="17">
+      <c r="F24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H24" s="16">
         <v>2</v>
       </c>
-      <c r="I24" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
+      <c r="I24" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <v>46061</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <v>69</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F25" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H25" s="18">
+      <c r="F25" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="17">
         <v>2</v>
       </c>
-      <c r="I25" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1892,49 +1927,49 @@
       <c r="E26" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H26" s="17">
+      <c r="F26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H26" s="16">
         <v>2</v>
       </c>
-      <c r="I26" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
+      <c r="I26" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="8">
         <v>46063</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>48</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H27" s="18">
+      <c r="F27" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H27" s="17">
         <v>2</v>
       </c>
-      <c r="I27" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1950,57 +1985,57 @@
       <c r="E28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F28" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H28" s="17">
+      <c r="F28" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H28" s="16">
         <v>2</v>
       </c>
-      <c r="I28" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
+      <c r="I28" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="13">
         <v>46065</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <v>17</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F29" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H29" s="18">
+      <c r="F29" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H29" s="17">
         <v>2</v>
       </c>
-      <c r="I29" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4">
         <v>46066</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>18</v>
+      <c r="C30" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>16</v>
@@ -2008,277 +2043,277 @@
       <c r="E30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H30" s="17">
+      <c r="F30" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H30" s="16">
         <v>2</v>
       </c>
-      <c r="I30" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
+      <c r="I30" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="13">
         <v>46067</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="14">
         <v>19</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H31" s="18">
+      <c r="F31" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H31" s="17">
         <v>2</v>
       </c>
-      <c r="I31" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>33</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>46101</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>35</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>19</v>
+      <c r="D32" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H32" s="17">
+      <c r="F32" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H32" s="16">
         <v>3</v>
       </c>
-      <c r="I32" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
+      <c r="I32" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
         <v>34</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="8">
         <v>46102</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="C33" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H33" s="18">
+      <c r="F33" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H33" s="17">
         <v>3</v>
       </c>
-      <c r="I33" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>35</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>46103</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <v>40</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H34" s="17">
+      <c r="E34" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H34" s="16">
         <v>3</v>
       </c>
-      <c r="I34" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
+      <c r="I34" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6">
         <v>36</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="8">
         <v>46120</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>36</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H35" s="18">
+      <c r="E35" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H35" s="17">
         <v>4</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="12">
+    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11">
         <v>37</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>46136</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="9">
         <v>37</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H36" s="17">
+      <c r="F36" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H36" s="16">
         <v>4</v>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="13">
+    <row r="37" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <v>38</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="8">
         <v>46198</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="7">
         <v>38</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H37" s="18">
+      <c r="F37" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H37" s="17">
         <v>6</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>39</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>46199</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="9">
         <v>39</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F38" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="17">
-        <v>2026</v>
-      </c>
-      <c r="H38" s="17">
+      <c r="F38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H38" s="16">
         <v>6</v>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="13">
+    <row r="39" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="12">
         <v>40</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="8">
         <v>46200</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="C39" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" s="18">
-        <v>2026</v>
-      </c>
-      <c r="H39" s="18">
+      <c r="F39" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="17">
+        <v>2026</v>
+      </c>
+      <c r="H39" s="17">
         <v>6</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="17">
         <v>2</v>
       </c>
     </row>
